--- a/guia1/CTF .xlsx
+++ b/guia1/CTF .xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arombola\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27484E3F-2C65-4F0A-B8BD-78C557A2E128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9996174-7309-4C1A-8BFC-4D01EA6E0617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E0DA0FA2-2813-4F59-A2F2-94752F84A99C}"/>
   </bookViews>
   <sheets>
     <sheet name="CTF" sheetId="1" r:id="rId1"/>
-    <sheet name="IPC" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="IPC" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="166">
   <si>
     <t>Detalle</t>
   </si>
@@ -466,6 +468,75 @@
   </si>
   <si>
     <t>INFO QUE VIENE DEL CTF DEL AÑO ANTERIOR</t>
+  </si>
+  <si>
+    <t>ALTA</t>
+  </si>
+  <si>
+    <t>BAJA</t>
+  </si>
+  <si>
+    <t>VO al cierre</t>
+  </si>
+  <si>
+    <t>AA al inicio</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>AA al cierre</t>
+  </si>
+  <si>
+    <t>CÍA</t>
+  </si>
+  <si>
+    <t>VU</t>
+  </si>
+  <si>
+    <t>GAN</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>IV = SUM (I, II, III)</t>
+  </si>
+  <si>
+    <t>FORM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SI ES BAJA, CALCULAR LA AMORT. DEL AÑO PASADO. </t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>valor residual</t>
+  </si>
+  <si>
+    <t>mes de alta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La idea es armar una planilla donde pegar todos los datos que nos da la cia, y que en otra planilla, me calcule todo eso, que reconozca si hay algun mismo activo fijo y si tiene alguna baja, que cargue la baja y si hay alta que le sume la alta. En caso que no tenga activo fijo, sumarlo a la planilla y asi ir calculando todo. </t>
+  </si>
+  <si>
+    <t>En la planilla de ipc, estaria buenisimo si puede tomarla de la web y se haga automaticamente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tambien hay que hacer una planilla de axi, que calcule todo como la de ctf y luego haga la comparacion en otra planilla a ver como evoluciona todo. </t>
+  </si>
+  <si>
+    <t>siempre es diciembre del año que estoy haciedno</t>
   </si>
 </sst>
 </file>
@@ -476,7 +547,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -552,8 +623,23 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -587,6 +673,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -683,7 +775,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -777,6 +869,25 @@
     <xf numFmtId="43" fontId="7" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="7" fillId="6" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -789,14 +900,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1146,7 +1251,7 @@
     <col min="13" max="13" width="28.08984375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="25.1796875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.1796875" customWidth="1"/>
+    <col min="16" max="16" width="41.7265625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.08984375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.81640625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="28.90625" bestFit="1" customWidth="1"/>
@@ -1160,18 +1265,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="L1" s="50">
+      <c r="L1" s="59">
         <v>2026</v>
       </c>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
+      <c r="R1" s="59"/>
+      <c r="S1" s="59"/>
+      <c r="T1" s="59"/>
+      <c r="U1" s="59"/>
       <c r="W1" s="46" t="s">
         <v>142</v>
       </c>
@@ -1185,16 +1290,16 @@
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="6"/>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="W2" s="48" t="s">
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="W2" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="49"/>
+      <c r="X2" s="58"/>
       <c r="Y2"/>
     </row>
     <row r="3" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -1294,7 +1399,7 @@
         <v>15200</v>
       </c>
       <c r="G4" s="12">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H4" s="15">
         <f>$L$1-YEAR(C4)</f>
@@ -1306,7 +1411,7 @@
       </c>
       <c r="J4" s="16">
         <f t="shared" ref="J4:J13" si="0">(YEAR(C4)+G4)-1</f>
-        <v>2013</v>
+        <v>2025</v>
       </c>
       <c r="L4" s="27">
         <f>+IF(H4&gt;G4,F4,0)+IF(H4&lt;=G4,F4/G4*H4)</f>
@@ -1357,9 +1462,9 @@
         <f>+M4-W4</f>
         <v>0</v>
       </c>
-      <c r="Z4" s="28">
+      <c r="Z4" s="28" t="str">
         <f>+IF(J4=$L$1-1,"agotó v.util LY",0)</f>
-        <v>0</v>
+        <v>agotó v.util LY</v>
       </c>
       <c r="AA4" s="28">
         <f>+IF(E4=$L$1,"ALTAS 2026",0)</f>
@@ -2218,6 +2323,12 @@
         <f>+SUM(N4:N13)</f>
         <v>152519.076</v>
       </c>
+      <c r="O14" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="P14" s="53" t="s">
+        <v>165</v>
+      </c>
       <c r="S14" s="31">
         <f>+SUM(S4:S13)</f>
         <v>2427287.4791991035</v>
@@ -2244,13 +2355,13 @@
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A15" s="51"/>
-      <c r="B15" s="51"/>
-      <c r="C15" s="51"/>
+      <c r="A15" s="47"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="47"/>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="53"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="49"/>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
       <c r="J15" s="13"/>
@@ -4933,6 +5044,437 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34D2C660-E5A5-46EC-B08C-4D23D6E1DB33}">
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="44.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="E2" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="G2" s="54" t="s">
+        <v>157</v>
+      </c>
+      <c r="H2" s="54" t="s">
+        <v>157</v>
+      </c>
+      <c r="I2" s="54" t="s">
+        <v>157</v>
+      </c>
+      <c r="J2" s="54" t="s">
+        <v>157</v>
+      </c>
+      <c r="K2" s="54" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="54"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="54"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="D5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F5" t="s">
+        <v>155</v>
+      </c>
+      <c r="G5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="10">
+        <v>234567</v>
+      </c>
+      <c r="B7" s="14">
+        <v>38127</v>
+      </c>
+      <c r="C7" s="12">
+        <v>10</v>
+      </c>
+      <c r="D7" s="11">
+        <v>15200</v>
+      </c>
+      <c r="E7" s="50"/>
+      <c r="F7" s="51">
+        <f>-D7</f>
+        <v>-15200</v>
+      </c>
+      <c r="G7" s="51">
+        <f>+SUM(D7:F7)</f>
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>158</v>
+      </c>
+      <c r="K7" s="51">
+        <f>+SUM(H7:J7)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="52">
+        <f>+G7-K7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="10">
+        <v>901887</v>
+      </c>
+      <c r="B8" s="14">
+        <v>38532</v>
+      </c>
+      <c r="C8" s="10">
+        <v>6</v>
+      </c>
+      <c r="D8" s="11">
+        <v>23208</v>
+      </c>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="51">
+        <f t="shared" ref="G8:G16" si="0">+SUM(D8:F8)</f>
+        <v>23208</v>
+      </c>
+      <c r="K8" s="51">
+        <f t="shared" ref="K8:K16" si="1">+SUM(H8:J8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="10">
+        <v>130145</v>
+      </c>
+      <c r="B9" s="14">
+        <v>40088</v>
+      </c>
+      <c r="C9" s="10">
+        <v>3</v>
+      </c>
+      <c r="D9" s="11">
+        <v>24295.040000000001</v>
+      </c>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="51">
+        <f t="shared" si="0"/>
+        <v>24295.040000000001</v>
+      </c>
+      <c r="K9" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="10">
+        <v>130145</v>
+      </c>
+      <c r="B10" s="14">
+        <v>43414</v>
+      </c>
+      <c r="C10" s="10">
+        <v>3</v>
+      </c>
+      <c r="D10" s="11">
+        <v>28650</v>
+      </c>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="51">
+        <f t="shared" si="0"/>
+        <v>28650</v>
+      </c>
+      <c r="K10" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="10">
+        <v>130146</v>
+      </c>
+      <c r="B11" s="14">
+        <v>44905</v>
+      </c>
+      <c r="C11" s="10">
+        <v>3</v>
+      </c>
+      <c r="D11" s="11">
+        <v>39801.19</v>
+      </c>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="51">
+        <f t="shared" si="0"/>
+        <v>39801.19</v>
+      </c>
+      <c r="K11" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="10">
+        <v>130147</v>
+      </c>
+      <c r="B12" s="14">
+        <v>45184</v>
+      </c>
+      <c r="C12" s="10">
+        <v>5</v>
+      </c>
+      <c r="D12" s="11">
+        <v>36102.5</v>
+      </c>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="51">
+        <f t="shared" si="0"/>
+        <v>36102.5</v>
+      </c>
+      <c r="K12" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="10">
+        <v>130148</v>
+      </c>
+      <c r="B13" s="14">
+        <v>45460</v>
+      </c>
+      <c r="C13" s="10">
+        <v>5</v>
+      </c>
+      <c r="D13" s="11">
+        <v>22382.44</v>
+      </c>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="51">
+        <f t="shared" si="0"/>
+        <v>22382.44</v>
+      </c>
+      <c r="K13" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" s="10">
+        <v>170002</v>
+      </c>
+      <c r="B14" s="14">
+        <v>45881</v>
+      </c>
+      <c r="C14" s="10">
+        <v>1</v>
+      </c>
+      <c r="D14" s="11">
+        <v>25000</v>
+      </c>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="51">
+        <f t="shared" si="0"/>
+        <v>25000</v>
+      </c>
+      <c r="K14" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" s="10">
+        <v>109835</v>
+      </c>
+      <c r="B15" s="14">
+        <v>46095</v>
+      </c>
+      <c r="C15" s="10">
+        <v>5</v>
+      </c>
+      <c r="D15" s="11">
+        <v>95432</v>
+      </c>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="51">
+        <f t="shared" si="0"/>
+        <v>95432</v>
+      </c>
+      <c r="K15" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" s="32">
+        <v>109892</v>
+      </c>
+      <c r="B16" s="33">
+        <v>46041</v>
+      </c>
+      <c r="C16" s="32">
+        <v>2</v>
+      </c>
+      <c r="D16" s="36">
+        <v>120000</v>
+      </c>
+      <c r="E16" s="50">
+        <v>20000</v>
+      </c>
+      <c r="F16" s="50"/>
+      <c r="G16" s="51">
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="K16" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="D17" s="52">
+        <f>SUM(D7:D16)</f>
+        <v>430071.17000000004</v>
+      </c>
+      <c r="E17" s="52">
+        <f t="shared" ref="E17:I17" si="2">SUM(E7:E16)</f>
+        <v>20000</v>
+      </c>
+      <c r="F17" s="52">
+        <f t="shared" si="2"/>
+        <v>-15200</v>
+      </c>
+      <c r="G17" s="52">
+        <f t="shared" si="2"/>
+        <v>434871.17000000004</v>
+      </c>
+      <c r="I17" s="52">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="52">
+        <f t="shared" ref="L17" si="3">SUM(L7:L16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I18" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="L18" s="55" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>164</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E57220-A1A6-49FA-88E1-912591FDC6B9}">
   <dimension ref="A1:C103"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6068,6 +6610,241 @@
 </worksheet>
 </file>
 
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001E3A188818E4D7438C041407C333926B" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="038f90ba40a4d9670c5faf12f3b1b830">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="fbc59c50-defa-4113-ae0c-5fda5a1279ac" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5a198744c0ec37866de87fc1e9fa5d8a" ns3:_="">
+    <xsd:import namespace="fbc59c50-defa-4113-ae0c-5fda5a1279ac"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="fbc59c50-defa-4113-ae0c-5fda5a1279ac" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceDateTaken" ma:index="8" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="12" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="13" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="fbc59c50-defa-4113-ae0c-5fda5a1279ac" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4BF811B-2732-4D3B-976A-7632EA411011}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fbc59c50-defa-4113-ae0c-5fda5a1279ac"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE28656C-17EC-4780-B442-D3879E91596D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB77E364-3B5A-4197-904C-6DE665EA219A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="fbc59c50-defa-4113-ae0c-5fda5a1279ac"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{ea60d57e-af5b-4752-ac57-3e4f28ca11dc}" enabled="1" method="Standard" siteId="{36da45f1-dd2c-4d1f-af13-5abe46b99921}" removed="0"/>
